--- a/output/full_scan/batch_seq7_2026-06-30.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-30.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1101.713347694778</v>
+        <v>1561.713347694777</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>345</v>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>71.1801994971367</v>
+        <v>71.18019955821759</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>24.31502928648122</v>
+        <v>24.3150292571671</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.051072986246377</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.7482383716490331</v>
+        <v>0.7482383712674503</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6658</v>
+        <v>6753</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>798.7653220909749</v>
+        <v>1164</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>234</v>
+        <v>136.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.88578379911461</v>
+        <v>64.39421756321573</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>29.16371582240138</v>
+        <v>15.22123300833733</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.530695953614947</v>
+        <v>5.340525767156733</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.802919087796637</v>
+        <v>1.59789500888214</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6753</v>
+        <v>6658</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>769</v>
+        <v>1023.765322090975</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>136.5</v>
+        <v>234</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.39421747488737</v>
+        <v>71.88578381581915</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.22123300833732</v>
+        <v>29.1637158422953</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.340525767156733</v>
+        <v>2.530695953614947</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.597895009549902</v>
+        <v>2.802919087567669</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6525</v>
+        <v>6691</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>764.355863390843</v>
+        <v>902.5647865616312</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>151</v>
+        <v>761</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.1453781499773</v>
+        <v>61.05996172255101</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.56553383353165</v>
+        <v>32.25466578279516</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5817164363742774</v>
+        <v>1.445198928201611</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.6811440942826987</v>
+        <v>8.794489972563881</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6651</v>
+        <v>6831</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>744.1268047379023</v>
+        <v>884.8853912506124</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>153.5</v>
+        <v>873</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.47710693447254</v>
+        <v>63.1716479967038</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30.24614092815111</v>
+        <v>27.1203621992819</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.991623061999898</v>
+        <v>1.499743107250949</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1460305218481572</v>
+        <v>2.96557307540278</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6757</v>
+        <v>6651</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>720.3793409384767</v>
+        <v>884.1268047379023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>62.3</v>
+        <v>153.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.9624439990592</v>
+        <v>57.47710699911797</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>35.99448285439715</v>
+        <v>30.24614092815111</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3854440372934277</v>
+        <v>0.991623061999898</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4394527915573087</v>
+        <v>-0.1460305220771101</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6719</v>
+        <v>6757</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>706.0461385407189</v>
+        <v>860.379340938477</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>270</v>
+        <v>62.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>58.18564256263549</v>
+        <v>60.96244434615844</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>38.55495887353207</v>
+        <v>35.99448318899256</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.110707675742345</v>
+        <v>0.3854440372934277</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.038689404850659</v>
+        <v>0.4394527901454317</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6742</v>
+        <v>6672</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>684.9739044760006</v>
+        <v>848.2131236411549</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>67.8</v>
+        <v>300</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.31273227719232</v>
+        <v>73.24795769209177</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>34.48879201259483</v>
+        <v>36.44961482921647</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4263112852770854</v>
+        <v>0.8450822231889045</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.1526336530562764</v>
+        <v>5.878120884162211</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6666</v>
+        <v>6525</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>667.1954600671863</v>
+        <v>829.355863390843</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>43.7</v>
+        <v>151</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.88956591115885</v>
+        <v>61.14537815186154</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>41.02016780755172</v>
+        <v>34.56553382900563</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4015869333127099</v>
+        <v>0.5817164363742774</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0775413370707369</v>
+        <v>0.6811440945307297</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6585</v>
+        <v>6584</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>663.8441645629875</v>
+        <v>820.6765780871214</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>130</v>
+        <v>734</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.72458773095982</v>
+        <v>59.80350207473858</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>54.59621758474736</v>
+        <v>15.09032958019739</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.2747929856726148</v>
+        <v>1.280826424944149</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.783332427423224</v>
+        <v>11.88048470152791</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6799</v>
+        <v>6589</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>663.839900049321</v>
+        <v>816.8710849695608</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>98.8</v>
+        <v>49.9</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>51.90022050177</v>
+        <v>68.11376498267987</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24.65029099032174</v>
+        <v>17.59079054778427</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5569075860311323</v>
+        <v>1.700664389786837</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1688499285767259</v>
+        <v>0.518059982205217</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6517</v>
+        <v>6666</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>662.1101107417624</v>
+        <v>807.1954600671862</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>73</v>
+        <v>43.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.08448980580965</v>
+        <v>61.88956606567061</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.46798722347743</v>
+        <v>41.02016790872193</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.546823637023674</v>
+        <v>0.4015869333127099</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.5303781021152711</v>
+        <v>0.0775413368990229</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6538</v>
+        <v>6725</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>661.5257308451213</v>
+        <v>799.9684101611376</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>131</v>
+        <v>349</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.15894507604911</v>
+        <v>58.32534506840657</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32.02901745592425</v>
+        <v>23.17751109792652</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.095502315978902</v>
+        <v>1.033684331355132</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.5736429099118405</v>
+        <v>2.574146385393813</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6725</v>
+        <v>6770</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>659.9684101611376</v>
+        <v>786.561163144489</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>349</v>
+        <v>79.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.32534503127596</v>
+        <v>56.18881809070952</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.1775109937602</v>
+        <v>25.44336518408556</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.033684331355132</v>
+        <v>0.9994469701986936</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.574146385966223</v>
+        <v>0.1933271871547042</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6494</v>
+        <v>6517</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>652.2329721397631</v>
+        <v>772.1101107417621</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.12320137437536</v>
+        <v>57.08448984055314</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>32.68040870495615</v>
+        <v>31.46798725803108</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.1911911486131445</v>
+        <v>0.546823637023674</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.1391165766584108</v>
+        <v>-0.530378102248835</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6672</v>
+        <v>6799</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>648.2131236411549</v>
+        <v>753.839900049321</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>300</v>
+        <v>98.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>73.247957684819</v>
+        <v>51.90022055099691</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>36.4496148360538</v>
+        <v>24.65029094212266</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8450822231889045</v>
+        <v>0.5569075860311323</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>5.878120884257584</v>
+        <v>0.1688499281760633</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6589</v>
+        <v>6790</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>646.8710849695608</v>
+        <v>739.5999285051172</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>49.9</v>
+        <v>40.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.11376491301554</v>
+        <v>62.78579128364566</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.59079053788463</v>
+        <v>21.98722580630625</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.700664389786837</v>
+        <v>1.408104935823644</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.518059982338771</v>
+        <v>0.1000707627799422</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6770</v>
+        <v>6531</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>646.561163144489</v>
+        <v>719.1036432347697</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>79.7</v>
+        <v>998</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.18881809007576</v>
+        <v>50.46948320671486</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.44336522613357</v>
+        <v>26.12787474118386</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.9994469701986936</v>
+        <v>0.718338922242337</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1933271871547042</v>
+        <v>-4.140743661418014</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6642</v>
+        <v>6573</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>623.299911778837</v>
+        <v>711.6697126593961</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>78.8</v>
+        <v>21.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45.9859037599234</v>
+        <v>71.52254971473133</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>37.95567797589301</v>
+        <v>25.00241439348666</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2998405091118716</v>
+        <v>1.192785442103274</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.728227558190292</v>
+        <v>0.4786399699783246</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6584</v>
+        <v>6719</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>620.6765780871212</v>
+        <v>706.0461385407189</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>734</v>
+        <v>270</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>59.80350206487637</v>
+        <v>58.18564258590497</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15.09032964331135</v>
+        <v>38.55495881350475</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.280826424944149</v>
+        <v>1.110707675742345</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>11.88048470143253</v>
+        <v>1.038689404850659</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6691</v>
+        <v>6698</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>617.5647865616311</v>
+        <v>701.9664511543174</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>761</v>
+        <v>43.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.059961713911</v>
+        <v>56.82315832455898</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>32.25466576532571</v>
+        <v>35.18905471124015</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.445198928201611</v>
+        <v>0.38549985879695</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>8.794489972563881</v>
+        <v>-0.0077313847230833</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6668</v>
+        <v>6526</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>609.9522432929656</v>
+        <v>683.5396256375782</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>38.95</v>
+        <v>670</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46.14556302338033</v>
+        <v>51.14073241225905</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.06263973607344</v>
+        <v>14.31219860868362</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2100983547158756</v>
+        <v>1.071157908847113</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.4806173285962569</v>
+        <v>-3.238940459119072</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6831</v>
+        <v>6625</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>609.8853912506124</v>
+        <v>683.0878247551309</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>873</v>
+        <v>78.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>63.1716479975089</v>
+        <v>61.67874929715525</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.12036212219358</v>
+        <v>31.27994057999728</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.499743107250949</v>
+        <v>0.4995007754500936</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.965573075326517</v>
+        <v>0.0807620353121527</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6531</v>
+        <v>6742</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>604.1036432347697</v>
+        <v>674.9739044760006</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>998</v>
+        <v>67.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>50.46948319478656</v>
+        <v>60.31273228511208</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.12787473604613</v>
+        <v>34.48879201746157</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.718338922242337</v>
+        <v>0.4263112852770854</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-4.140743660273145</v>
+        <v>-0.1526336529990288</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6698</v>
+        <v>6645</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>601.9664511543174</v>
+        <v>669.9150119012108</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>43.3</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.82315831159289</v>
+        <v>64.36643980635586</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>35.18905468116707</v>
+        <v>50.22284124584513</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.38549985879695</v>
+        <v>0.2502263404342885</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0077313846849276</v>
+        <v>0.1313644619980054</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6790</v>
+        <v>6585</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>599.5999285051172</v>
+        <v>663.8441645629875</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>40.8</v>
+        <v>130</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.78579156698335</v>
+        <v>57.72458766074903</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.98722575600725</v>
+        <v>54.59621760262128</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.408104935823644</v>
+        <v>0.2747929856726148</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1000707626750024</v>
+        <v>-1.783332427614008</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6684</v>
+        <v>6538</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>593.7792955286835</v>
+        <v>661.5257308451213</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>58.7</v>
+        <v>131</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>63.47561333312326</v>
+        <v>60.1589450926335</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>36.74363602169083</v>
+        <v>32.02901745592425</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5740753406192982</v>
+        <v>1.095502315978902</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.9143875345126666</v>
+        <v>0.573642909701964</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6526</v>
+        <v>6829</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>568.5396256375782</v>
+        <v>657.6240344208927</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>670</v>
+        <v>222.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.14073235814368</v>
+        <v>55.51386343740501</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.31219860984679</v>
+        <v>15.05815330640194</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.071157908847113</v>
+        <v>1.055142351603079</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-3.238940457783519</v>
+        <v>2.100525132459475</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6645</v>
+        <v>6664</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>554.9150119012108</v>
+        <v>654.5625402753121</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>16</v>
+        <v>391</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>64.36643976223826</v>
+        <v>49.29866695718477</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>50.22284125011554</v>
+        <v>24.57697130223515</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2502263404342885</v>
+        <v>0.943958436427161</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,84 +2054,84 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1313644620838624</v>
+        <v>1.534498038262381</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6806</v>
+        <v>6670</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>548.7768356926886</v>
+        <v>652.2343610454949</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>3.51</v>
+        <v>255.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>31.69502790452029</v>
+        <v>42.17246716230514</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32.59319629483674</v>
+        <v>29.56904743449532</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.171879911433359</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4112821526563897</v>
+        <v>-4.618457564483466</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6625</v>
+        <v>6494</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>543.0878247551308</v>
+        <v>652.2329721397631</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>78.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.67874919583698</v>
+        <v>57.12320140248971</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.27994039681722</v>
+        <v>32.6804085958084</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4995007754500936</v>
+        <v>0.1911911486131445</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.08076203523583619</v>
+        <v>-0.1391165766965643</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6670</v>
+        <v>6788</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>537.2343610454949</v>
+        <v>650.1133705436679</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>255.5</v>
+        <v>430.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>42.17246706234462</v>
+        <v>50.06096414746015</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.56904745370905</v>
+        <v>8.070796797488267</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.171879911433359</v>
+        <v>0.2871948406531289</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-4.618457564769674</v>
+        <v>-0.9428911219301694</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6654</v>
+        <v>6642</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>530.4571853181014</v>
+        <v>623.299911778837</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>185</v>
+        <v>78.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.57657185510291</v>
+        <v>45.98590375803764</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46.74136795917073</v>
+        <v>37.955677952473</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2011434638033316</v>
+        <v>0.2998405091118716</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-4.125319166100002</v>
+        <v>-1.728227558113973</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6756</v>
+        <v>6579</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>515.2601561236983</v>
+        <v>619.3705283419009</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>157.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>49.6664623958213</v>
+        <v>49.97646946334473</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.83132186978308</v>
+        <v>23.64573351454458</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4193734607410133</v>
+        <v>0.303080775499393</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.7218582710972929</v>
+        <v>-2.218872679468925</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6573</v>
+        <v>6556</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>511.669712659396</v>
+        <v>613.1861033480394</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>21.7</v>
+        <v>72.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>71.52254970808977</v>
+        <v>54.33380522920739</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.0024143957617</v>
+        <v>35.31141096847037</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.192785442103274</v>
+        <v>0.4028319083154576</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.4786399699783246</v>
+        <v>-0.1523152244923498</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6788</v>
+        <v>6781</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>510.1133705436676</v>
+        <v>613.1612061675822</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>430.5</v>
+        <v>1180</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.06096415434372</v>
+        <v>52.243753889458</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>8.070796800383826</v>
+        <v>11.65877729977166</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2871948406531289</v>
+        <v>1.108803749689663</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.9428911220255536</v>
+        <v>-1.186925937334246</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6716</v>
+        <v>6668</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>506.5636391512314</v>
+        <v>609.9522432929656</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>92.8</v>
+        <v>38.95</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45.37715499077302</v>
+        <v>46.14556304963822</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22.74202071517853</v>
+        <v>26.06263973533352</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4075191592593683</v>
+        <v>0.2100983547158756</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.9801411832609233</v>
+        <v>-0.4806173287011968</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6640</v>
+        <v>6821</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>493.2064024339113</v>
+        <v>605.8226131447639</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1025</v>
+        <v>64.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>37.27922946977442</v>
+        <v>52.09403271910486</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24.83462650709204</v>
+        <v>18.57488112452391</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5763332157408728</v>
+        <v>1.403641865673746</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2241127135331169</v>
+        <v>-0.8008240186817679</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6667</v>
+        <v>6684</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>492.6941820694816</v>
+        <v>593.7792955286835</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>268</v>
+        <v>58.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.95688422253434</v>
+        <v>63.47561338517117</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.87620977422502</v>
+        <v>36.74363598969549</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3954711524583499</v>
+        <v>0.5740753406192982</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.838081788500848</v>
+        <v>0.914387534884716</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6821</v>
+        <v>6505</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>490.8226131447639</v>
+        <v>588.8203842089016</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>64.5</v>
+        <v>55.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.09403263515055</v>
+        <v>55.18289531063706</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.57488128686245</v>
+        <v>13.66784831516107</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.403641865673746</v>
+        <v>0.6834335792461161</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.8008240187390079</v>
+        <v>0.2406235744245507</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6579</v>
+        <v>6743</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>484.3705283419009</v>
+        <v>585.7973938983922</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>157.5</v>
+        <v>30.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.97646942341747</v>
+        <v>57.0830562547073</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.64573347745371</v>
+        <v>22.69504657741257</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.303080775499393</v>
+        <v>0.927564359441352</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.218872679087323</v>
+        <v>0.0604963565827788</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6556</v>
+        <v>6803</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>473.1861033480394</v>
+        <v>583.5617842387549</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>72.5</v>
+        <v>289</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.33379348063134</v>
+        <v>55.61563998164723</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>35.31140560398403</v>
+        <v>28.82513506720938</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4028319083154576</v>
+        <v>0.7177137128340642</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.1523152096294557</v>
+        <v>0.2617908836879171</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6695</v>
+        <v>6548</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>468.388209357615</v>
+        <v>573.7578943090949</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>59.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.00172164688458</v>
+        <v>54.01715002119701</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>28.78697491659083</v>
+        <v>41.59997752014094</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3463643244174831</v>
+        <v>0.7198520208482563</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2069545926543798</v>
+        <v>-1.814470207994337</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6498</v>
+        <v>6560</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>468.1587432897487</v>
+        <v>568.89625458519</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>38.95</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40.00506684758722</v>
+        <v>52.49872599229966</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.71590493302743</v>
+        <v>24.02944615915072</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5559636373266865</v>
+        <v>0.3273348199252815</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.37042165368496</v>
+        <v>0.1121313738952247</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6664</v>
+        <v>6624</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>464.5625402753121</v>
+        <v>559.6240895239614</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>391</v>
+        <v>40.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.29866692588137</v>
+        <v>50.85584265342323</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.57697133111253</v>
+        <v>10.34528220170778</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.943958436427161</v>
+        <v>0.0410145355513994</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.534498038739418</v>
+        <v>0.5044340556176947</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6548</v>
+        <v>6692</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>458.7578943090949</v>
+        <v>558.6956404893132</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>83.90000000000001</v>
+        <v>26.35</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.01715000574185</v>
+        <v>46.23264273235477</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>41.59997755059701</v>
+        <v>16.98778607335512</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7198520208482563</v>
+        <v>1.053395311631174</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.814470207975258</v>
+        <v>0.2072697207141759</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6560</v>
+        <v>6581</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>453.8962545851901</v>
+        <v>550.7915168828976</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>38.95</v>
+        <v>107</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.49872597121304</v>
+        <v>45.52821728832625</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24.02944618122349</v>
+        <v>11.65476366883544</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3273348199252815</v>
+        <v>0.9608484050548136</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,48 +3008,48 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1121313741909551</v>
+        <v>-0.2980426910141741</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6743</v>
+        <v>6806</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>445.7973938983922</v>
+        <v>548.7768356926886</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>30.3</v>
+        <v>3.51</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.08305612051161</v>
+        <v>31.69502810632723</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.69504651517979</v>
+        <v>32.5931961682865</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.927564359441352</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0604963566590965</v>
+        <v>0.4112821525352812</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6781</v>
+        <v>6582</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>443.1612061675817</v>
+        <v>548.2007542152858</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1180</v>
+        <v>33</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.2437537960195</v>
+        <v>64.72310168170553</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11.65877720585532</v>
+        <v>31.77559254325888</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.108803749689663</v>
+        <v>0.8449896371703897</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.186925934472306</v>
+        <v>0.1777995926506515</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6811</v>
+        <v>6654</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>435.7382955700149</v>
+        <v>530.4571853181014</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>38.98642571069011</v>
+        <v>58.57657183467311</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21.35345025275683</v>
+        <v>46.74136810468016</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2603939817680276</v>
+        <v>0.2011434638033316</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-3.874792435937697</v>
+        <v>-4.125319165489458</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6803</v>
+        <v>6550</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>423.5617842387548</v>
+        <v>526.2871311626793</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>289</v>
+        <v>13.55</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>55.61563985559557</v>
+        <v>45.59459629208124</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.82513511743665</v>
+        <v>28.22096879806939</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7177137128340642</v>
+        <v>0.8668569511336487</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2617908838786946</v>
+        <v>0.1866630097582022</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6505</v>
+        <v>6532</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>418.8203842089016</v>
+        <v>525.4521094733483</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>55.1</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>55.18289534210334</v>
+        <v>46.09575860795583</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.66784834413795</v>
+        <v>18.54791830101805</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6834335792461161</v>
+        <v>0.4124972027747811</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.2406235742146812</v>
+        <v>-0.1083247727179566</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6581</v>
+        <v>6515</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>415.7915168828974</v>
+        <v>523.6915583121116</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107</v>
+        <v>8085</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.52821714118856</v>
+        <v>39.13809508483493</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11.65476364491606</v>
+        <v>19.26464288394054</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9608484050548136</v>
+        <v>0.6719263833369611</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2980426907279778</v>
+        <v>-124.9163012912268</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6592</v>
+        <v>6720</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>414.7667934137359</v>
+        <v>517.9378367547031</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>58.7</v>
+        <v>140</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>29.25035150698384</v>
+        <v>37.22286742814589</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.32908862541676</v>
+        <v>30.7276525467657</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.078074128085923</v>
+        <v>0.536803140460013</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.6041925603256428</v>
+        <v>-0.3156075751432361</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6515</v>
+        <v>6756</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>413.653898534496</v>
+        <v>515.2601561236983</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>8085</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>39.13809508483493</v>
+        <v>49.66646245089419</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.26464285564084</v>
+        <v>21.83132188148216</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6695054457111064</v>
+        <v>0.4193734607410133</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-124.9163012925616</v>
+        <v>-0.7218582712880737</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6829</v>
+        <v>6782</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>412.6240344208928</v>
+        <v>515.1698926784879</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>222.5</v>
+        <v>196</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>55.51386342010092</v>
+        <v>51.22977764450872</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.05815331543857</v>
+        <v>7.822858708570592</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.055142351603079</v>
+        <v>0.5311874190650262</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>2.100525132554882</v>
+        <v>0.465313393706253</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6792</v>
+        <v>6667</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>411.4831606860256</v>
+        <v>512.6941820694816</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>63</v>
+        <v>268</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>42.91987137441385</v>
+        <v>48.9568843651155</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.04012817975332</v>
+        <v>11.87620980720801</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3048931865665605</v>
+        <v>0.3954711524583499</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.9745911520326318</v>
+        <v>-1.83808179155357</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6679</v>
+        <v>6763</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>410.7298698744889</v>
+        <v>509.6211478579089</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>263.5</v>
+        <v>47.45</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>40.27754589159037</v>
+        <v>53.26205798118379</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.08352534046004</v>
+        <v>18.33350806525038</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3978409956819914</v>
+        <v>0.5840903166352107</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.231106982964217</v>
+        <v>-0.050929830010655</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6532</v>
+        <v>6716</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>410.4521094733482</v>
+        <v>506.5636391512314</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.09575856158426</v>
+        <v>45.37715504449328</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.54791825028423</v>
+        <v>22.74202077572342</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4124972027747811</v>
+        <v>0.4075191592593683</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1083247725462563</v>
+        <v>-0.9801411836806738</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6582</v>
+        <v>6640</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>408.2007542152856</v>
+        <v>493.2064024339113</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>33</v>
+        <v>1025</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>64.72310163792434</v>
+        <v>37.27922947221415</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>31.77559254314548</v>
+        <v>24.83462654667265</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.8449896371703897</v>
+        <v>0.5763332157408728</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1777995926506515</v>
+        <v>0.2241127130562006</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6727</v>
+        <v>6568</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>403.3065245047664</v>
+        <v>488.0918825976237</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>428.5</v>
+        <v>162.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46.46759443599469</v>
+        <v>33.28657688459772</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.90276686940614</v>
+        <v>31.05635922229622</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5005487863239183</v>
+        <v>0.3964825441541887</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.892165427360709</v>
+        <v>-0.7678450719782752</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6720</v>
+        <v>6504</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>402.9378367547031</v>
+        <v>483.1739982436265</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>37.2228673093778</v>
+        <v>39.76416197417245</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>30.72765258483197</v>
+        <v>16.82695158023806</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.536803140460013</v>
+        <v>1.077731971082034</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.3156075749524438</v>
+        <v>0.1126747052999368</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6570</v>
+        <v>6486</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>394.5825801896049</v>
+        <v>472.6392277846506</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>50.3</v>
+        <v>81.3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.62637591701338</v>
+        <v>44.33988138194238</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>25.4857610745104</v>
+        <v>12.55722320757778</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3465372907852751</v>
+        <v>0.6743676056183594</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.232210535228063</v>
+        <v>0.003046519709269</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6510</v>
+        <v>6739</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>381.6497538440767</v>
+        <v>471.5977799192323</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>3035</v>
+        <v>1040</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>38.71660294856561</v>
+        <v>38.5600191738329</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.34858586346293</v>
+        <v>11.37705356492206</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.084140061461948</v>
+        <v>0.7010625537100117</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-44.53597774417543</v>
+        <v>-8.705512033584654</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6690</v>
+        <v>6695</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>378.9420642505061</v>
+        <v>468.388209357615</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>162</v>
+        <v>59.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>35.01335412707112</v>
+        <v>54.00172170284202</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.23682614960636</v>
+        <v>28.78697488626348</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2716244123381117</v>
+        <v>0.3463643244174831</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-2.280311389473705</v>
+        <v>0.2069545926543798</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6568</v>
+        <v>6498</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>378.0918825976237</v>
+        <v>468.1587432897487</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>162.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>33.28657684504844</v>
+        <v>40.00506689204983</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>31.05635917235165</v>
+        <v>24.71590496063353</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3964825441541887</v>
+        <v>0.5559636373266865</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.7678450717874732</v>
+        <v>-1.370421654104707</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6541</v>
+        <v>6530</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>371.702008530824</v>
+        <v>467.4583126181201</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>40.1</v>
+        <v>87.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.4523616296387</v>
+        <v>37.25270715936563</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.51219576905307</v>
+        <v>21.43334959092918</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6658693845554526</v>
+        <v>0.3240340852985373</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1726282279524899</v>
+        <v>-1.229693639249832</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6735</v>
+        <v>6512</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>363.3292362360909</v>
+        <v>461.5382382750778</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>87</v>
+        <v>19.95</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>38.39499405895065</v>
+        <v>52.34257433744122</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12.64991318484626</v>
+        <v>7.507095811071714</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4644625174748527</v>
+        <v>0.5383745530241545</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.392230856798335</v>
+        <v>0.2841953265273886</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6739</v>
+        <v>6655</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>361.5977799192319</v>
+        <v>456.9307292852637</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1040</v>
+        <v>123</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.56001916416957</v>
+        <v>50.90760170281831</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.37705354587729</v>
+        <v>12.07890566521264</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7010625537100117</v>
+        <v>0.9456088380069938</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-8.705512036351386</v>
+        <v>1.955550665287268</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6830</v>
+        <v>6789</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>359.4216668029381</v>
+        <v>455.9277943112417</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>496.5</v>
+        <v>513</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37.85039873517302</v>
+        <v>49.24857795767353</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.784651795549</v>
+        <v>14.99008246352443</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.945969936329946</v>
+        <v>0.6897857800302524</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0050867397405625</v>
+        <v>0.0121809524155536</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6643</v>
+        <v>6811</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>357.8374489870449</v>
+        <v>455.7382955700149</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>476</v>
+        <v>208</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.62036233326494</v>
+        <v>38.98642579853395</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.41033781300818</v>
+        <v>21.35345035723107</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5641730730053762</v>
+        <v>0.2603939817680276</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.5480584647353055</v>
+        <v>-3.874792435079124</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6486</v>
+        <v>6534</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>357.6392277846506</v>
+        <v>453.4789858143834</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>81.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.33988128195039</v>
+        <v>45.65697000547131</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.55722317546887</v>
+        <v>13.61028482122446</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6743676056183594</v>
+        <v>0.3154290258532514</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0030465197665056</v>
+        <v>0.0691125507409857</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6530</v>
+        <v>6614</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>357.4583126181204</v>
+        <v>441.3989563108443</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>87.5</v>
+        <v>39.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>37.25270713853458</v>
+        <v>46.81205978609896</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21.43334958836002</v>
+        <v>15.8684454872737</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3240340852985373</v>
+        <v>1.042183005449371</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.229693639268906</v>
+        <v>-0.0361404721192739</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6782</v>
+        <v>6679</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>355.1698926784879</v>
+        <v>430.7298698744889</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>196</v>
+        <v>263.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,49 +4421,49 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.22977744931784</v>
+        <v>40.27754594370283</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7.822858782895897</v>
+        <v>19.08352542657768</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5311874190650262</v>
+        <v>0.3978409956819914</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.4653133942786693</v>
+        <v>-1.231106983727445</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6763</v>
+        <v>6732</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>349.621147857909</v>
+        <v>428.7004724198085</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>47.45</v>
+        <v>166.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>53.26205786963347</v>
+        <v>52.48369073530657</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.33350811500021</v>
+        <v>17.90199589800739</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5840903166352107</v>
+        <v>0.6272933588835299</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0509298299343339</v>
+        <v>0.5111242150046251</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6504</v>
+        <v>6592</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>348.1739982436265</v>
+        <v>414.7667934137359</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>36</v>
+        <v>58.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>39.76416231054775</v>
+        <v>29.25035141827117</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.82695158023806</v>
+        <v>28.32908887523948</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.077731971082034</v>
+        <v>2.078074128085923</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1126747051854614</v>
+        <v>-0.6041925600012845</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6789</v>
+        <v>6792</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>345.9277943112417</v>
+        <v>411.4831606860256</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>513</v>
+        <v>63</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>49.24857794259747</v>
+        <v>42.91987132492488</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14.99008250906428</v>
+        <v>25.04012824529819</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6897857800302524</v>
+        <v>0.3048931865665605</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0121809528925732</v>
+        <v>-0.9745911518609108</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6692</v>
+        <v>6606</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>343.6956404893132</v>
+        <v>407.5474148790532</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>26.35</v>
+        <v>24.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.2326426585877</v>
+        <v>42.36566514315169</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.98778606618285</v>
+        <v>18.41665987369608</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.053395311631174</v>
+        <v>0.2837972172034425</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.2072697208095715</v>
+        <v>-0.1497876536943765</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6655</v>
+        <v>6727</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>341.9307292852637</v>
+        <v>403.3065245047664</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>123</v>
+        <v>428.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.90760169556273</v>
+        <v>46.4675944366376</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.07890571566335</v>
+        <v>14.90276691809526</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9456088380069938</v>
+        <v>0.5005487863239183</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.955550665573455</v>
+        <v>-2.89216542730346</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6534</v>
+        <v>6510</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>338.4789858143833</v>
+        <v>401.6618761704696</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>3035</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.65697005517632</v>
+        <v>38.71660295970558</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.61028477872678</v>
+        <v>17.34858596122553</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3154290258532514</v>
+        <v>1.085352294101249</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0691125504166368</v>
+        <v>-44.53597774780059</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6550</v>
+        <v>6605</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>336.2871311626793</v>
+        <v>395.8139871154892</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>13.55</v>
+        <v>136</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.594596793421</v>
+        <v>45.05062399194832</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>28.22096845970978</v>
+        <v>14.59622854651097</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8668569511336487</v>
+        <v>1.175732430381916</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1866630090713437</v>
+        <v>-1.064057848344159</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6624</v>
+        <v>6570</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>334.6240895239613</v>
+        <v>394.5825801896049</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>40.5</v>
+        <v>50.3</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.85584265525471</v>
+        <v>42.62637595456636</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10.34528198771058</v>
+        <v>25.48576110235808</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.0410145355513994</v>
+        <v>0.3465372907852751</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.5044340555986104</v>
+        <v>-1.23221053530438</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6805</v>
+        <v>6735</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>330.9679652415299</v>
+        <v>383.3292362360909</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1680</v>
+        <v>87</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.79751401362168</v>
+        <v>38.39499405895065</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.84819544555041</v>
+        <v>12.6499131537278</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8189241031587813</v>
+        <v>0.4644625174748527</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-15.84074720400251</v>
+        <v>-0.3922308567887915</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6577</v>
+        <v>6690</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>327.9844199990558</v>
+        <v>378.9420642505061</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>162</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>27.68032812763985</v>
+        <v>35.01335417621701</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.58303243403146</v>
+        <v>19.23682593381817</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4984419999055757</v>
+        <v>0.2716244123381117</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.6930772002718286</v>
+        <v>-2.280311388996712</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6512</v>
+        <v>6541</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>321.5382382750778</v>
+        <v>371.702008530824</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>19.95</v>
+        <v>40.1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.34257433878643</v>
+        <v>48.45236175793107</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.507095810659681</v>
+        <v>16.51219579061532</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5383745530241545</v>
+        <v>0.6658693845554526</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2841953265273886</v>
+        <v>-0.1726282281242078</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6761</v>
+        <v>6669</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>319.939674355745</v>
+        <v>371.0887615277093</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>185.5</v>
+        <v>4635</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,49 +5057,49 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.70097171686914</v>
+        <v>43.59632870789746</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.08599066365126</v>
+        <v>18.50648962321814</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2706629356596233</v>
+        <v>1.112598666062822</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-2.792222106446226</v>
+        <v>-71.67479860695101</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6598</v>
+        <v>6838</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>319.2931172299786</v>
+        <v>368.9463088029392</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>22.85</v>
+        <v>24.35</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>34.22980754298823</v>
+        <v>42.4215349968221</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21.20277111490075</v>
+        <v>14.02657571046577</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7141653568391427</v>
+        <v>0.5731771662298814</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.2296609386305958</v>
+        <v>0.0095509324139942</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6732</v>
+        <v>6708</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>313.7004724198086</v>
+        <v>366.3149357899342</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>166.5</v>
+        <v>40.15</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>52.48369069862653</v>
+        <v>49.71338592197085</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.90199585348931</v>
+        <v>15.22873301994981</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6272933588835299</v>
+        <v>0.919293491666797</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.5111242157678162</v>
+        <v>0.1224623839043602</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6614</v>
+        <v>6830</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>306.3989563108444</v>
+        <v>359.4216668029381</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>39.8</v>
+        <v>496.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.81206011113015</v>
+        <v>37.85039874617585</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.8684454415657</v>
+        <v>20.78465172316168</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.042183005449371</v>
+        <v>0.945969936329946</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.036140472157432</v>
+        <v>-0.0050867394543914</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6588</v>
+        <v>6643</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>291.9003088546164</v>
+        <v>357.8374489870449</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>88.2</v>
+        <v>476</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>30.08746051331969</v>
+        <v>40.62036249460407</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.36249277262892</v>
+        <v>22.41033791289864</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4751751379661414</v>
+        <v>0.5641730730053762</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.107202153484027</v>
+        <v>-0.5480584717946151</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6796</v>
+        <v>6641</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>291.8620469059928</v>
+        <v>351.6331108639957</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>56.9</v>
+        <v>18</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>37.08315531086998</v>
+        <v>41.84146649910604</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>29.55711819420293</v>
+        <v>16.45615162355315</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5279435445391598</v>
+        <v>0.3708073991268625</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.024144854026787</v>
+        <v>-0.0363376321282976</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6754</v>
+        <v>6674</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>291.1649982161907</v>
+        <v>336.9388224228873</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>44.5</v>
+        <v>17.3</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.00413603262268</v>
+        <v>45.89598320246154</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20.04066048026013</v>
+        <v>18.43434284130274</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3572879746000475</v>
+        <v>1.303982852625488</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0951771575605412</v>
+        <v>-0.0149152016723312</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6823</v>
+        <v>6657</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>290.3000884204722</v>
+        <v>336.6656324234591</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>36.4</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.09254492452971</v>
+        <v>46.9056126034025</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20.48207222019018</v>
+        <v>22.1180050454108</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6789768736148355</v>
+        <v>0.2846884266703383</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.3326559457715756</v>
+        <v>0.2130780993941181</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6722</v>
+        <v>6577</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>286.9128125766408</v>
+        <v>327.9844199990558</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>34.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>33.55115930173677</v>
+        <v>27.68032814741566</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.78193457961333</v>
+        <v>24.58303240413047</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.749627018783073</v>
+        <v>0.4984419999055757</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3128497438730402</v>
+        <v>-0.6930772002145928</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6605</v>
+        <v>6761</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>280.8139871154892</v>
+        <v>319.939674355745</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>136</v>
+        <v>185.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.05062408138311</v>
+        <v>42.70097173857698</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>14.59622852340485</v>
+        <v>17.08599063342363</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.175732430381916</v>
+        <v>0.2706629356596233</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.064057848916551</v>
+        <v>-2.792222106617941</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6771</v>
+        <v>6598</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>273.9095039382515</v>
+        <v>319.2931172299786</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>39.6</v>
+        <v>22.85</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>36.72992497438906</v>
+        <v>34.22980757837841</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>21.08047483387102</v>
+        <v>21.20277121269377</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.052734704020664</v>
+        <v>0.7141653568391427</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2970448598102576</v>
+        <v>-0.2296609386401354</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6606</v>
+        <v>6805</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>267.5474148790532</v>
+        <v>315.9679652415304</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>24.9</v>
+        <v>1680</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.36566509738513</v>
+        <v>42.79751402972344</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.41665987369608</v>
+        <v>13.84819544555041</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.2837972172034425</v>
+        <v>0.8189241031587813</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1497876537611558</v>
+        <v>-15.84074720390695</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6669</v>
+        <v>6588</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>256.068599703694</v>
+        <v>291.9003088546164</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>4635</v>
+        <v>88.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>43.59632867670338</v>
+        <v>30.08746050727252</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.5064896010627</v>
+        <v>18.36249274884446</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.110979289182641</v>
+        <v>0.4751751379661414</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-71.6747986002724</v>
+        <v>-1.107202153426795</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6708</v>
+        <v>6796</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>251.3149357899343</v>
+        <v>291.8620469059928</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>40.15</v>
+        <v>56.9</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>49.71338597762659</v>
+        <v>37.08315542851393</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.22873304763837</v>
+        <v>29.5571182043699</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.919293491666797</v>
+        <v>0.5279435445391598</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1224623837708072</v>
+        <v>-0.0241448542366611</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6533</v>
+        <v>6754</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>245.2597619413199</v>
+        <v>291.1649982161908</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>197</v>
+        <v>44.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.54033981229686</v>
+        <v>45.00413604727053</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.69981668353082</v>
+        <v>20.04066063889508</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3457211559292221</v>
+        <v>0.3572879746000475</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.7246790887222838</v>
+        <v>-0.0951771574842268</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6741</v>
+        <v>6823</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>243.9003832316536</v>
+        <v>290.3000884204722</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>60.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.31933759229256</v>
+        <v>39.09254497684834</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.886975626385956</v>
+        <v>20.48207227892281</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6072339555768299</v>
+        <v>0.6789768736148355</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1138662904405338</v>
+        <v>0.332655945933757</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6641</v>
+        <v>6722</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>236.6331108639958</v>
+        <v>286.9128125766408</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>18</v>
+        <v>34.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.84146631195511</v>
+        <v>33.55115930994945</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.45615155070876</v>
+        <v>26.78193457987933</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3708073991268625</v>
+        <v>1.749627018783073</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0363376321092189</v>
+        <v>-0.3128497438825739</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6597</v>
+        <v>6794</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>229.3503480441439</v>
+        <v>286.3080498225327</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>67</v>
+        <v>79.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.9064506670833</v>
+        <v>47.15817893783291</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.30414244035065</v>
+        <v>13.77834202464919</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3435309727884605</v>
+        <v>0.96045197740113</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.4695541781437044</v>
+        <v>-0.0772807425066713</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6674</v>
+        <v>6771</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>221.9388224228873</v>
+        <v>273.9095039382516</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17.3</v>
+        <v>39.6</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.89598307786399</v>
+        <v>36.72992499929646</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.43434272863628</v>
+        <v>21.08047480969158</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.303982852625488</v>
+        <v>1.052734704020664</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0149152015483143</v>
+        <v>-0.2970448597720971</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6680</v>
+        <v>6591</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>213.5264421554854</v>
+        <v>251.8291703577904</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>48.3</v>
+        <v>53.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>49.79114641159823</v>
+        <v>42.05031061245455</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>4.768472649572433</v>
+        <v>21.77457113771408</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6553222133374483</v>
+        <v>0.3932612416531606</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.3275076761352374</v>
+        <v>-0.2292299758009166</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6840</v>
+        <v>6533</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>213.5210303066063</v>
+        <v>245.2597619413199</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>62.5</v>
+        <v>197</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.37523138631306</v>
+        <v>41.54033991419958</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.44183053549614</v>
+        <v>12.69981671976924</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3800669489638368</v>
+        <v>0.3457211559292221</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.576716535953076</v>
+        <v>-0.724679089294666</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6552</v>
+        <v>6741</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>210.4162270047188</v>
+        <v>243.9003832316536</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>30</v>
+        <v>60.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.91061068195832</v>
+        <v>43.31933767925055</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.40607521535734</v>
+        <v>9.886975662388451</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3757958696245683</v>
+        <v>0.6072339555768299</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1946973225808217</v>
+        <v>-0.11386629057409</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6838</v>
+        <v>6840</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>208.9463088029408</v>
+        <v>233.5210303066063</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>24.35</v>
+        <v>62.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.42153493994742</v>
+        <v>42.37523142797316</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.02657571620927</v>
+        <v>15.44183050549564</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5731771662298814</v>
+        <v>0.3800669489638368</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0095509323662945</v>
+        <v>-0.5767165360389299</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6776</v>
+        <v>6561</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>206.5549633235651</v>
+        <v>232.7806650761631</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>53.9</v>
+        <v>332</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,49 +6276,49 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>29.34609284911627</v>
+        <v>38.43357328006229</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.83020528505134</v>
+        <v>17.9026563483335</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4465414552163511</v>
+        <v>2.130413995169852</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.7321443876547286</v>
+        <v>-1.140816076921776</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6706</v>
+        <v>6597</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>201.8301798788077</v>
+        <v>229.3503480441439</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>149.5</v>
+        <v>67</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.42440049612802</v>
+        <v>45.90645044974426</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.24071284734582</v>
+        <v>10.30414243916219</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5716911054501435</v>
+        <v>0.3435309727884605</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-3.753957512540921</v>
+        <v>-0.4695541786206803</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6671</v>
+        <v>6776</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>198.7255737686909</v>
+        <v>221.5549633235651</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>24.35</v>
+        <v>53.9</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>23.89723057598391</v>
+        <v>29.346092868067</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>28.05859939149434</v>
+        <v>15.83020529770328</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6593235124194005</v>
+        <v>0.4465414552163511</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0429259767962876</v>
+        <v>-0.7321443876547286</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6689</v>
+        <v>6807</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>196.2975170183748</v>
+        <v>218.0347142825476</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>63.5</v>
+        <v>33.45</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.47361000039804</v>
+        <v>46.29211568016933</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.83187427209418</v>
+        <v>18.80913363323647</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4762130552567505</v>
+        <v>0.6039504398269078</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.5507604459638527</v>
+        <v>0.1102842457572875</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6546</v>
+        <v>6689</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>192.9373141492974</v>
+        <v>216.2975170183754</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.7</v>
+        <v>63.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.16659460467332</v>
+        <v>35.47361006806503</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.47637393212191</v>
+        <v>14.83187434734512</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3851724157723339</v>
+        <v>0.4762130552567505</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.9665822125708144</v>
+        <v>-0.550760446192808</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6835</v>
+        <v>6680</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>185.7005817051665</v>
+        <v>213.5264421554853</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>34.6</v>
+        <v>48.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>31.42708611758508</v>
+        <v>49.79114640999671</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.98998291892898</v>
+        <v>4.768472714032188</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3371209088847083</v>
+        <v>0.6553222133374483</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1692316127008405</v>
+        <v>0.3275076760398405</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6768</v>
+        <v>6552</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>184.9162692559029</v>
+        <v>210.4162270047188</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>74.7</v>
+        <v>30</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>28.1295071327785</v>
+        <v>46.91061070699574</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.6934068165252</v>
+        <v>13.40607517797255</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4934597331266823</v>
+        <v>0.3757958696245683</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-1.935246148300355</v>
+        <v>-0.1946973225999009</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6591</v>
+        <v>6671</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>151.8291703577905</v>
+        <v>198.7255737686909</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>53.5</v>
+        <v>24.35</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.05031052707865</v>
+        <v>23.89723056742072</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>21.77457116723497</v>
+        <v>28.05859934859052</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3932612416531606</v>
+        <v>0.6593235124194005</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2292299759058613</v>
+        <v>-0.0429259767962876</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6558</v>
+        <v>6546</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>148.1332702346313</v>
+        <v>192.9373141492974</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>29.4</v>
+        <v>69.7</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.95893971694154</v>
+        <v>42.16659471474266</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>21.83829113969147</v>
+        <v>15.47637394750274</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3937523865213057</v>
+        <v>0.3851724157723339</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.3492338405695561</v>
+        <v>-0.9665822127616041</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6657</v>
+        <v>6706</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>146.665632423459</v>
+        <v>191.8301798788077</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>36.4</v>
+        <v>149.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.90561249085544</v>
+        <v>40.42440051324596</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>22.11800505675178</v>
+        <v>17.24071280132607</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2846884266703383</v>
+        <v>0.5716911054501435</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2130780996421462</v>
+        <v>-3.753957512579099</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6794</v>
+        <v>6835</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>126.3080498225328</v>
+        <v>185.7005817051665</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>79.5</v>
+        <v>34.6</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>47.1581789131632</v>
+        <v>31.42708626441491</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.77834196053935</v>
+        <v>19.98998292761271</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.96045197740113</v>
+        <v>0.3371209088847083</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0772807425066713</v>
+        <v>-0.1692316128725489</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6561</v>
+        <v>6768</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>117.7806650761632</v>
+        <v>184.9162692559027</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>332</v>
+        <v>74.7</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.43357317045604</v>
+        <v>28.12950732959822</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>17.90265631357807</v>
+        <v>19.6934068548758</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>2.130413995169852</v>
+        <v>0.4934597331266823</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-1.140816075872441</v>
+        <v>-1.935246148014163</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6807</v>
+        <v>6558</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>78.03471428254764</v>
+        <v>168.1332702346313</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>33.45</v>
+        <v>29.4</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.29211583615665</v>
+        <v>43.95893977658413</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.8091328471753</v>
+        <v>21.83829122356257</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6039504398269078</v>
+        <v>0.3937523865213057</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,11 +6930,11 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.110284245184898</v>
+        <v>-0.3492338407221926</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
